--- a/public/templates/test_input/Input_bao_cao_49.xlsx
+++ b/public/templates/test_input/Input_bao_cao_49.xlsx
@@ -759,20 +759,18 @@
     <row r="4">
       <c r="A4" s="27" t="inlineStr">
         <is>
-          <t>04/07/2026</t>
+          <t>12/07/2026</t>
         </is>
       </c>
-      <c r="B4" s="1" t="inlineStr">
-        <is>
-          <t>Ca 1</t>
-        </is>
+      <c r="B4" s="1" t="n">
+        <v>3</v>
       </c>
       <c r="C4" s="15" t="n">
         <v>1</v>
       </c>
       <c r="D4" s="11" t="inlineStr">
         <is>
-          <t>PX Khai thác 2</t>
+          <t>PX Đào lò</t>
         </is>
       </c>
       <c r="E4" s="1" t="inlineStr">
@@ -781,43 +779,47 @@
         </is>
       </c>
       <c r="F4" s="2" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G4" s="28" t="n">
-        <v>1094</v>
+        <v>1125</v>
       </c>
       <c r="H4" s="28" t="n">
-        <v>10</v>
+        <v>11.8</v>
       </c>
       <c r="I4" s="28" t="n">
-        <v>1.7</v>
+        <v>6.2</v>
       </c>
       <c r="J4" s="28" t="n">
-        <v>9.199999999999999</v>
+        <v>11.1</v>
       </c>
       <c r="K4" s="28" t="n">
-        <v>5.7</v>
+        <v>0.8</v>
       </c>
       <c r="L4" s="28" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="M4" s="28" t="n">
-        <v>6</v>
+        <v>3.1</v>
       </c>
       <c r="N4" s="28" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="O4" s="28" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="P4" s="28" t="n">
-        <v>15.1</v>
+        <v>12.5</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="R4" s="3" t="inlineStr"/>
-      <c r="S4" s="12" t="inlineStr"/>
+      <c r="S4" s="12" t="inlineStr">
+        <is>
+          <t>Điều kiện sản xuất ổn định.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="27" t="n"/>
